--- a/kahoot_family_20.xlsx
+++ b/kahoot_family_20.xlsx
@@ -85,10 +85,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">時光機出發！第一個單字 "family" 是什麼意思？</t>
         </is>
@@ -123,10 +120,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">用英文介紹「這是我的爸爸」，爸爸是哪個單字？</t>
         </is>
@@ -161,10 +155,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">穿越回古羅馬！"family" 小時候的照片是哪個字？</t>
         </is>
@@ -199,10 +190,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">"mother" 的「小時候照片」（古英文）長這樣？</t>
         </is>
@@ -237,10 +225,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">古英文 brōþor 裡有個怪字母 "þ"，它長得像？</t>
         </is>
@@ -275,10 +260,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve">遇到 "daughter" 裡的 "gh"，要怎麼念？</t>
         </is>
@@ -313,10 +295,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>7</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve">"son"（兒子）和哪個字念起來一模一樣？</t>
         </is>
@@ -351,10 +330,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>8</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">"dad" 這個字是怎麼來的？</t>
         </is>
@@ -389,10 +365,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>9</v>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">"grandfather" 是混血字，由哪兩部分合起來？</t>
         </is>
@@ -427,10 +400,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t xml:space="preserve">一個哥哥加一個弟弟，英文要怎麼說？</t>
         </is>
@@ -465,10 +435,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>11</v>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">叔叔、舅舅、姨丈，英文可以全部叫？</t>
         </is>
@@ -503,10 +470,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>12</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑、阿姨，英文可以全部叫？</t>
         </is>
@@ -541,10 +505,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>13</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">叔叔的兒子，對「我」來說英文是？</t>
         </is>
@@ -579,10 +540,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>14</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">我是阿姨，姊姊的兒子對「我」來說是？</t>
         </is>
@@ -617,10 +575,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">想說「這是我的家人」，正確的英文是？</t>
         </is>
@@ -655,10 +610,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>16</v>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">看到媽媽，開心地叫「嗨，媽媽！」，英文是？</t>
         </is>
@@ -693,10 +645,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>17</v>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve">"uncle" 走過：拉丁語→法文→英文，法文是？</t>
         </is>
@@ -731,10 +680,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t xml:space="preserve">哥哥的女兒，對「我」來說是？</t>
         </is>
@@ -769,10 +715,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t xml:space="preserve">哪一個單字是「奶奶、外婆」的意思？</t>
         </is>
@@ -807,10 +750,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>20</v>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve">"sister" 以前有兩種寫法，後來混成 sister，因為？</t>
         </is>

--- a/kahoot_family_20.xlsx
+++ b/kahoot_family_20.xlsx
@@ -21,28 +21,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add questions, at least two answer alternatives, time limit and choose correct answers (at least one). Have fun creating your awesome quiz!</t>
+          <t xml:space="preserve">家人單字 暖身 20 題（由 words/_build_kahoot.js 產生，勿手改）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remember: questions have a limit of 95 characters and answers can have 60 characters max. If several answers are correct, separate them with a comma.</t>
+          <t xml:space="preserve">題目上限 95 字、選項上限 60 字。時間只能是 5/10/20/30/60/90/120 秒。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">See an example question below (don't forget to overwrite this with your first question!)</t>
+          <t xml:space="preserve">匯入後，請到編輯器把第 2、5、6、9、12、18 題的 Points 改成 Double points（雙倍分數）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">And remember, if you're not using Excel you need to export to .xlsx format before you upload to Kahoot!</t>
+          <t xml:space="preserve">若不是用 Excel 編輯，上傳前要先另存成 .xlsx。</t>
         </is>
       </c>
     </row>
@@ -87,31 +87,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">時光機出發！第一個單字 "family" 是什麼意思？</t>
+          <t xml:space="preserve">很久以前的 family，連誰都算在裡面？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">家庭；家人</t>
+          <t xml:space="preserve">家裡幫忙做事的人</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">朋友</t>
+          <t xml:space="preserve">隔壁的鄰居</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">學校</t>
+          <t xml:space="preserve">只有爸爸和媽媽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">動物</t>
+          <t xml:space="preserve">學校的同學</t>
         </is>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -122,101 +122,101 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">用英文介紹「這是我的爸爸」，爸爸是哪個單字？</t>
+          <t xml:space="preserve">有人說 family 是 Father And Mother I Love You 拼出來的。這是真的嗎？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">father / dad</t>
+          <t xml:space="preserve">真的，造這個字的人取的</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brother</t>
+          <t xml:space="preserve">真的，英國國王規定的</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">uncle</t>
+          <t xml:space="preserve">假的，是後來的人倒著湊出來的</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">cousin</t>
+          <t xml:space="preserve">真的，英文課本第一課就有</t>
         </is>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿越回古羅馬！"family" 小時候的照片是哪個字？</t>
+          <t xml:space="preserve">dad 這個字是怎麼來的？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mōdor</t>
+          <t xml:space="preserve">把 father 剪短</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">familia</t>
+          <t xml:space="preserve">老師發明的</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fæder</t>
+          <t xml:space="preserve">從法國借來的</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunu</t>
+          <t xml:space="preserve">寶寶自己先發出來的音</t>
         </is>
       </c>
       <c r="G11">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">"mother" 的「小時候照片」（古英文）長這樣？</t>
+          <t xml:space="preserve">為什麼全世界的「媽媽」幾乎都用 m 開頭（mother、mom、媽媽、mama）？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">mōdor</t>
+          <t xml:space="preserve">ma 是寶寶最早發得出來的音</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dohtor</t>
+          <t xml:space="preserve">大家互相抄來抄去</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">nepos</t>
+          <t xml:space="preserve">因為有人規定</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">familia</t>
+          <t xml:space="preserve">因為 m 最好寫</t>
         </is>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -227,66 +227,66 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">古英文 brōþor 裡有個怪字母 "þ"，它長得像？</t>
+          <t xml:space="preserve">daughter 中間的 gh，以前的人怎麼處理？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">一面小旗子</t>
+          <t xml:space="preserve">以前唸成 f</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">一顆太陽</t>
+          <t xml:space="preserve">以前會發出聲音，後來才不唸</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">一條魚</t>
+          <t xml:space="preserve">以前根本沒有這兩個字母</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">一朵花</t>
+          <t xml:space="preserve">從古到今都不唸</t>
         </is>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">遇到 "daughter" 裡的 "gh"，要怎麼念？</t>
+          <t xml:space="preserve">哪一個是「daughter 的 gh 以前真的有聲音」最有力的證據？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">念「嘎」</t>
+          <t xml:space="preserve">沒有證據，只是傳說</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">不用念，跳過去</t>
+          <t xml:space="preserve">德文 Tochter、荷蘭文 dochter 的 ch 到今天還唸得出來</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">念「喝」</t>
+          <t xml:space="preserve">因為字典上這樣寫</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">念「夫」</t>
+          <t xml:space="preserve">因為 gh 很難唸</t>
         </is>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -297,101 +297,101 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">"son"（兒子）和哪個字念起來一模一樣？</t>
+          <t xml:space="preserve">husband 裡面的 hus，就是今天的哪一個字？</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sun（太陽）</t>
+          <t xml:space="preserve">his（他的）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">song（歌）</t>
+          <t xml:space="preserve">house（房子）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">soon（很快）</t>
+          <t xml:space="preserve">nurse（護士）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">some（一些）</t>
+          <t xml:space="preserve">bus（公車）</t>
         </is>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">"dad" 這個字是怎麼來的？</t>
+          <t xml:space="preserve">以前的 wīf（也就是 wife），可以用在誰身上？</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">father 的縮寫</t>
+          <t xml:space="preserve">只有老人家</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">從拉丁語來的</t>
+          <t xml:space="preserve">每個女生都可以</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">老師發明的</t>
+          <t xml:space="preserve">只有結婚的女生</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶寶先叫出來的</t>
+          <t xml:space="preserve">只有當媽媽的人</t>
         </is>
       </c>
       <c r="G16">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">"grandfather" 是混血字，由哪兩部分合起來？</t>
+          <t xml:space="preserve">uncle 最早只有一個意思，是下面哪一個？</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">grand-（法文）＋father</t>
+          <t xml:space="preserve">舅舅（媽媽的兄弟）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">grand＋brother</t>
+          <t xml:space="preserve">叔叔（爸爸的弟弟）</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">grand＋son</t>
+          <t xml:space="preserve">姑丈</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">兩個 grand</t>
+          <t xml:space="preserve">伯伯（爸爸的哥哥）</t>
         </is>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -402,31 +402,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">一個哥哥加一個弟弟，英文要怎麼說？</t>
+          <t xml:space="preserve">中文有姑姑、阿姨、伯母、舅媽，英文要用幾個字？</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">two fathers</t>
+          <t xml:space="preserve">四個，每個都不一樣</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">two brothers</t>
+          <t xml:space="preserve">一個就夠：aunt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">two cousins</t>
+          <t xml:space="preserve">三個</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">two uncles</t>
+          <t xml:space="preserve">兩個</t>
         </is>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -437,31 +437,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">叔叔、舅舅、姨丈，英文可以全部叫？</t>
+          <t xml:space="preserve">今天的 sister 是怎麼來的？</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">brother</t>
+          <t xml:space="preserve">從法國借來的</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">nephew</t>
+          <t xml:space="preserve">把 brother 改一個字母</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">uncle</t>
+          <t xml:space="preserve">英國人唸 sweostor、維京人唸 systir，住久了唸成 sister</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">cousin</t>
+          <t xml:space="preserve">老師取的</t>
         </is>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -472,276 +472,276 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑、阿姨，英文可以全部叫？</t>
+          <t xml:space="preserve">grandfather 前面的 grand，是從哪裡借來的？</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">aunt / auntie</t>
+          <t xml:space="preserve">日語</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">niece</t>
+          <t xml:space="preserve">英文本來就有</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sister</t>
+          <t xml:space="preserve">維京人帶來的</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">mother</t>
+          <t xml:space="preserve">法語</t>
         </is>
       </c>
       <c r="G20">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">叔叔的兒子，對「我」來說英文是？</t>
+          <t xml:space="preserve">brother 以前寫成 brōþor，那個 þ 相當於今天的哪兩個字母？</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">cousin</t>
+          <t xml:space="preserve">ph</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">brother</t>
+          <t xml:space="preserve">ch</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">nephew</t>
+          <t xml:space="preserve">th</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">son</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="G21">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">我是阿姨，姊姊的兒子對「我」來說是？</t>
+          <t xml:space="preserve">想說「我哥哥」和「我弟弟」，英文怎麼分？</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">son（兒子）</t>
+          <t xml:space="preserve">加 big / small</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">nephew（外甥）</t>
+          <t xml:space="preserve">用兩個完全不同的字</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">brother（兄弟）</t>
+          <t xml:space="preserve">都是 brother，要分就加 older / younger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">cousin（堂表親）</t>
+          <t xml:space="preserve">一個是 brother，一個是 bro</t>
         </is>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">想說「這是我的家人」，正確的英文是？</t>
+          <t xml:space="preserve">son 和 sun 的關係是？</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is my family.</t>
+          <t xml:space="preserve">唸起來不一樣</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is my friend.</t>
+          <t xml:space="preserve">son 是 sun 的縮寫</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is my school.</t>
+          <t xml:space="preserve">唸起來一模一樣，拼法和意思都不一樣</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is my uncle.</t>
+          <t xml:space="preserve">是同一個字</t>
         </is>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">看到媽媽，開心地叫「嗨，媽媽！」，英文是？</t>
+          <t xml:space="preserve">我哥哥的女兒，對我來說英文是？</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hi, Mom!</t>
+          <t xml:space="preserve">sister</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hi, Dad!</t>
+          <t xml:space="preserve">niece</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hi, Son!</t>
+          <t xml:space="preserve">cousin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hi, Aunt!</t>
+          <t xml:space="preserve">daughter</t>
         </is>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">"uncle" 走過：拉丁語→法文→英文，法文是？</t>
+          <t xml:space="preserve">我阿姨的小孩，對我來說英文是？</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">oncle</t>
+          <t xml:space="preserve">nephew</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">amita</t>
+          <t xml:space="preserve">brother</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">nepos</t>
+          <t xml:space="preserve">niece</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosin</t>
+          <t xml:space="preserve">cousin</t>
         </is>
       </c>
       <c r="G25">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">哥哥的女兒，對「我」來說是？</t>
+          <t xml:space="preserve">nephew 最早寫成 nepos，那時候可以用在誰身上？</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">niece（姪女）</t>
+          <t xml:space="preserve">只有姪子</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">daughter（女兒）</t>
+          <t xml:space="preserve">任何小孩都可以</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">sister（姊妹）</t>
+          <t xml:space="preserve">只有外甥</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">aunt（阿姨）</t>
+          <t xml:space="preserve">孫子、姪子、外甥都可以</t>
         </is>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">哪一個單字是「奶奶、外婆」的意思？</t>
+          <t xml:space="preserve">parent 最早寫成 parens，意思是？</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">grandmother</t>
+          <t xml:space="preserve">把孩子生下來的人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">grandfather</t>
+          <t xml:space="preserve">管這個家的人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">nephew</t>
+          <t xml:space="preserve">家裡最老的人</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">niece</t>
+          <t xml:space="preserve">教小孩的人</t>
         </is>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -752,35 +752,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">"sister" 以前有兩種寫法，後來混成 sister，因為？</t>
+          <t xml:space="preserve">「一位家長」和「兩位家長」，英文分別怎麼寫？</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">太陽照到它</t>
+          <t xml:space="preserve">a parent ／ parents</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">老師改的</t>
+          <t xml:space="preserve">parent ／ parent</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">從法文借來的</t>
+          <t xml:space="preserve">a parents ／ parent</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">兩邊的人住一起，拼法混成</t>
+          <t xml:space="preserve">a parent ／ parenties</t>
         </is>
       </c>
       <c r="G28">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>

--- a/kahoot_family_20.xlsx
+++ b/kahoot_family_20.xlsx
@@ -35,7 +35,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">匯入後，請到編輯器把第 2、5、6、9、12、18 題的 Points 改成 Double points（雙倍分數）。</t>
+          <t xml:space="preserve">匯入後，請到編輯器把第 2、5、6、9、12、18 題的 Points 改成 Double points（分數 ✕ 2）。</t>
         </is>
       </c>
     </row>

--- a/kahoot_family_20.xlsx
+++ b/kahoot_family_20.xlsx
@@ -132,7 +132,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">真的，英國國王規定的</t>
+          <t xml:space="preserve">真的，是英國小朋友發明的口訣</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">真的，英文課本第一課就有</t>
+          <t xml:space="preserve">真的，每個字母各代表一個英文字</t>
         </is>
       </c>
       <c r="G10">
@@ -232,7 +232,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">以前唸成 f</t>
+          <t xml:space="preserve">以前唸成 g</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -312,7 +312,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">nurse（護士）</t>
+          <t xml:space="preserve">hug（抱抱）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -457,7 +457,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">老師取的</t>
+          <t xml:space="preserve">從德文 Schwester 借來的</t>
         </is>
       </c>
       <c r="G19">
@@ -477,7 +477,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">日語</t>
+          <t xml:space="preserve">德文</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">加 big / small</t>
+          <t xml:space="preserve">加 old / young</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">a parent ／ parents</t>
+          <t xml:space="preserve">a parent ／ two parents</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">parent ／ parent</t>
+          <t xml:space="preserve">a parent ／ two parent</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">a parents ／ parent</t>
+          <t xml:space="preserve">a parents ／ two parent</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">a parent ／ parenties</t>
+          <t xml:space="preserve">parent ／ two parents</t>
         </is>
       </c>
       <c r="G28">

--- a/kahoot_family_20.xlsx
+++ b/kahoot_family_20.xlsx
@@ -162,12 +162,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">把 father 剪短</t>
+          <t xml:space="preserve">father 唸太快，就變成 dad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">老師發明的</t>
+          <t xml:space="preserve">從中文的「爹」變來的</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">因為 m 最好寫</t>
+          <t xml:space="preserve">因為各國都跟英文學的</t>
         </is>
       </c>
       <c r="G12">
